--- a/data/trans_dic/IP42B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>La persona sustentadora principal recibe una pensión</t>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,33</t>
+          <t>0,0; 28,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 50,44</t>
+          <t>8,83; 49,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 27,71</t>
+          <t>2,71; 26,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,2</t>
+          <t>0,0; 23,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,73; 65,55</t>
+          <t>19,6; 66,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 34,29</t>
+          <t>3,3; 32,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,17</t>
+          <t>0,0; 20,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 49,7</t>
+          <t>19,43; 48,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 22,43</t>
+          <t>5,84; 23,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 35,42</t>
+          <t>3,82; 31,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 27,13</t>
+          <t>7,66; 27,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 24,88</t>
+          <t>5,56; 24,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,28</t>
+          <t>0,0; 15,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 25,15</t>
+          <t>6,95; 26,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 16,29</t>
+          <t>3,16; 16,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 18,68</t>
+          <t>3,33; 18,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 23,24</t>
+          <t>9,47; 22,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 16,66</t>
+          <t>5,17; 17,01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,28</t>
+          <t>0,0; 30,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,04</t>
+          <t>0,0; 21,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,98</t>
+          <t>0,0; 19,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,96</t>
+          <t>0,0; 29,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,89</t>
+          <t>0,0; 13,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,78</t>
+          <t>0,0; 11,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 18,07</t>
+          <t>2,12; 16,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,22</t>
+          <t>0,0; 11,85</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 37,92</t>
+          <t>4,6; 38,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,77; 44,41</t>
+          <t>10,82; 44,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,26</t>
+          <t>0,0; 17,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,78</t>
+          <t>0,0; 21,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 18,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 27,36</t>
+          <t>4,88; 27,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 20,91</t>
+          <t>3,94; 20,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 25,53</t>
+          <t>6,66; 26,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 18,48</t>
+          <t>4,24; 17,96</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,8</t>
+          <t>0,0; 77,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 58,02</t>
+          <t>10,2; 61,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,96</t>
+          <t>0,0; 22,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,07</t>
+          <t>0,0; 37,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,49</t>
+          <t>0,0; 18,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,15</t>
+          <t>0,0; 31,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 44,43</t>
+          <t>8,42; 42,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,01</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 26,36</t>
+          <t>3,11; 26,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,62</t>
+          <t>0,0; 40,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,87</t>
+          <t>0,0; 25,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 28,81</t>
+          <t>2,85; 27,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,8</t>
+          <t>0,0; 42,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,09</t>
+          <t>1,59; 12,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 23,28</t>
+          <t>4,31; 23,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 24,77</t>
+          <t>2,62; 24,7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,2</t>
+          <t>0,0; 13,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,71; 33,78</t>
+          <t>10,77; 32,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 20,92</t>
+          <t>3,84; 21,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 26,68</t>
+          <t>4,79; 26,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,65; 34,19</t>
+          <t>12,26; 34,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,22</t>
+          <t>0,0; 11,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 17,12</t>
+          <t>4,44; 16,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,8; 30,45</t>
+          <t>14,2; 29,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,07</t>
+          <t>3,29; 12,6</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,04</t>
+          <t>0,0; 18,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 14,75</t>
+          <t>1,63; 14,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 17,54</t>
+          <t>3,36; 18,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,11; 35,07</t>
+          <t>9,93; 35,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,32</t>
+          <t>1,66; 13,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 16,62</t>
+          <t>1,83; 16,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,92; 22,92</t>
+          <t>7,01; 22,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,28</t>
+          <t>2,68; 11,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,13</t>
+          <t>3,83; 12,79</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,94</t>
+          <t>5,59; 13,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,54; 20,23</t>
+          <t>11,22; 20,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,02</t>
+          <t>5,65; 12,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,93</t>
+          <t>4,31; 11,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,09; 18,63</t>
+          <t>10,14; 18,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,64</t>
+          <t>5,11; 10,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,77</t>
+          <t>5,68; 10,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,86</t>
+          <t>12,05; 18,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,07</t>
+          <t>6,03; 10,32</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5696</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8877</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2750</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1133; 6333</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>475; 4585</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3925</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2665; 9037</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>652; 6412</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5241</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5134; 12832</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2176; 8572</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2575</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5230</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4485</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10399</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7971</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>630; 5206</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2574; 9130</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1881; 8442</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3301</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2427; 9138</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1356; 7047</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1261; 7130</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6487; 15749</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3968; 13057</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4892</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3401</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3619</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4345</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3301</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4711</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>657; 4966</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5090</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4682</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3946</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3043</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5345</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>672; 5598</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026; 8294</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4471</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3936</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3547</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1452; 8213</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1294; 6797</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2554; 10024</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2322; 9843</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3826</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2578</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1005; 6056</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3556</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3140</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4082</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2634</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1528; 7780</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4067</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2878</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>643; 5431</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4165</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3156</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>454; 4431</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4578</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>635; 4879</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1133; 6290</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>605; 5711</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1352</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8255</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4107</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5459</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>16495</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4122</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4340; 12953</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1292; 7299</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1383; 7777</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4570; 12773</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4966</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2653; 9675</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>11019; 23255</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2555; 9788</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3947</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>6979</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>6558</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4398</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>602; 5179</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1544; 8409</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2724; 9608</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>724; 6075</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>738; 6568</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3610; 11691</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2157; 9519</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>3306; 11042</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>12496</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>28224</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>17029</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>54618</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>34596</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>7602; 18744</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>20048; 36695</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>11426; 24573</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>6922; 17956</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>19076; 35275</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11986; 24817</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>16854; 32322</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>44175; 66638</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>26344; 45078</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP42B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,29</t>
+          <t>0,0; 29,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 49,38</t>
+          <t>8,41; 46,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 26,19</t>
+          <t>2,55; 25,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,98</t>
+          <t>0,0; 24,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,6; 66,47</t>
+          <t>20,4; 65,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 32,45</t>
+          <t>3,23; 31,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,09</t>
+          <t>0,0; 20,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,43; 48,57</t>
+          <t>19,46; 49,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 23,0</t>
+          <t>5,81; 23,2</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 31,56</t>
+          <t>3,99; 34,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 27,16</t>
+          <t>7,55; 27,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 24,95</t>
+          <t>5,53; 24,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,48</t>
+          <t>0,0; 15,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 26,18</t>
+          <t>7,39; 27,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 16,41</t>
+          <t>3,12; 17,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 18,85</t>
+          <t>3,36; 18,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 22,98</t>
+          <t>9,36; 22,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 17,01</t>
+          <t>6,0; 16,89</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,24</t>
+          <t>0,0; 30,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,05</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,89</t>
+          <t>0,0; 22,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,33</t>
+          <t>0,0; 29,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,33</t>
+          <t>0,0; 13,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,63</t>
+          <t>0,0; 10,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 16,04</t>
+          <t>2,07; 16,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,85</t>
+          <t>0,0; 10,12</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 38,33</t>
+          <t>4,46; 37,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 44,28</t>
+          <t>10,62; 44,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,83</t>
+          <t>0,0; 18,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,57</t>
+          <t>0,0; 18,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,05</t>
+          <t>0,0; 14,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 27,62</t>
+          <t>4,89; 28,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 20,69</t>
+          <t>2,61; 21,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 26,12</t>
+          <t>6,62; 24,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 17,96</t>
+          <t>4,05; 18,21</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,42</t>
+          <t>0,0; 79,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 61,46</t>
+          <t>7,25; 59,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,68</t>
+          <t>0,0; 22,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,88</t>
+          <t>0,0; 37,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,54</t>
+          <t>0,0; 15,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,74</t>
+          <t>0,0; 31,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,42; 42,88</t>
+          <t>8,32; 41,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 26,26</t>
+          <t>3,04; 24,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,18</t>
+          <t>0,0; 34,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,7</t>
+          <t>0,0; 25,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,27 +1248,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 27,8</t>
+          <t>2,85; 28,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,25</t>
+          <t>0,0; 42,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 12,22</t>
+          <t>1,61; 14,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 23,91</t>
+          <t>4,34; 26,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 24,7</t>
+          <t>2,64; 24,82</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,32</t>
+          <t>0,0; 14,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,77; 32,13</t>
+          <t>10,67; 32,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 21,72</t>
+          <t>3,89; 21,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 26,96</t>
+          <t>4,85; 26,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 34,25</t>
+          <t>12,44; 34,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>1,32; 11,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 16,18</t>
+          <t>4,45; 17,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,2; 29,97</t>
+          <t>14,35; 30,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,6</t>
+          <t>3,24; 12,74</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,26</t>
+          <t>0,0; 17,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,05</t>
+          <t>1,6; 13,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,32</t>
+          <t>3,31; 18,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,93; 35,01</t>
+          <t>9,98; 34,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 13,95</t>
+          <t>1,57; 14,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,25</t>
+          <t>1,62; 15,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 22,69</t>
+          <t>8,01; 23,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 11,84</t>
+          <t>2,56; 11,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 12,79</t>
+          <t>4,01; 13,25</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,78</t>
+          <t>5,84; 13,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,22; 20,53</t>
+          <t>11,87; 20,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 12,16</t>
+          <t>6,03; 12,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,17</t>
+          <t>4,26; 10,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,14; 18,76</t>
+          <t>10,34; 18,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,58</t>
+          <t>4,91; 10,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,89</t>
+          <t>5,84; 11,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,17</t>
+          <t>11,94; 18,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,32</t>
+          <t>6,01; 10,41</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2750</t>
+          <t>0; 2833</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1133; 6333</t>
+          <t>1079; 6012</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>475; 4585</t>
+          <t>446; 4452</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3925</t>
+          <t>0; 4012</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2665; 9037</t>
+          <t>2773; 8961</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>652; 6412</t>
+          <t>639; 6161</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5241</t>
+          <t>0; 5417</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5134; 12832</t>
+          <t>5141; 13057</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2176; 8572</t>
+          <t>2164; 8647</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>630; 5206</t>
+          <t>658; 5711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2574; 9130</t>
+          <t>2538; 9173</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1881; 8442</t>
+          <t>1870; 8385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 3398</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2427; 9138</t>
+          <t>2579; 9484</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1356; 7047</t>
+          <t>1339; 7621</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1261; 7130</t>
+          <t>1271; 7024</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6487; 15749</t>
+          <t>6417; 15588</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3968; 13057</t>
+          <t>4606; 12969</t>
         </is>
       </c>
     </row>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4892</t>
+          <t>0; 4937</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 3619</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3619</t>
+          <t>0; 4128</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2207,27 +2207,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4345</t>
+          <t>0; 4352</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 3284</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4711</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>657; 4966</t>
+          <t>641; 5005</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5090</t>
+          <t>0; 4348</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>672; 5598</t>
+          <t>651; 5432</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026; 8294</t>
+          <t>1988; 8357</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4471</t>
+          <t>0; 4715</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3936</t>
+          <t>0; 3449</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3547</t>
+          <t>0; 2817</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1452; 8213</t>
+          <t>1455; 8436</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1294; 6797</t>
+          <t>859; 7213</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2554; 10024</t>
+          <t>2540; 9567</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2322; 9843</t>
+          <t>2219; 9981</t>
         </is>
       </c>
     </row>
@@ -2513,17 +2513,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2578</t>
+          <t>0; 2647</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1005; 6056</t>
+          <t>714; 5866</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3556</t>
+          <t>0; 3590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,27 +2533,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3140</t>
+          <t>0; 3139</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4082</t>
+          <t>0; 3345</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2634</t>
+          <t>0; 2622</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1528; 7780</t>
+          <t>1510; 7439</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4067</t>
+          <t>0; 4701</t>
         </is>
       </c>
     </row>
@@ -2676,17 +2676,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>643; 5431</t>
+          <t>629; 5067</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4165</t>
+          <t>0; 3579</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3156</t>
+          <t>0; 3144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2696,27 +2696,27 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>454; 4431</t>
+          <t>455; 4587</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4578</t>
+          <t>0; 4632</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>635; 4879</t>
+          <t>641; 5774</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1133; 6290</t>
+          <t>1141; 6977</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>605; 5711</t>
+          <t>610; 5739</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4122</t>
+          <t>0; 4601</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4340; 12953</t>
+          <t>4302; 12935</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1292; 7299</t>
+          <t>1307; 7106</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1383; 7777</t>
+          <t>1400; 7717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4570; 12773</t>
+          <t>4640; 12889</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4966</t>
+          <t>584; 5007</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2653; 9675</t>
+          <t>2663; 10182</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11019; 23255</t>
+          <t>11134; 23312</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2555; 9788</t>
+          <t>2515; 9899</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4398</t>
+          <t>0; 4265</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>602; 5179</t>
+          <t>590; 5053</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1544; 8409</t>
+          <t>1519; 8368</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2724; 9608</t>
+          <t>2739; 9484</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>724; 6075</t>
+          <t>684; 6473</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>738; 6568</t>
+          <t>656; 6233</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3610; 11691</t>
+          <t>4127; 12068</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2157; 9519</t>
+          <t>2061; 9140</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3306; 11042</t>
+          <t>3465; 11439</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>7602; 18744</t>
+          <t>7944; 18363</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20048; 36695</t>
+          <t>21221; 37511</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11426; 24573</t>
+          <t>12180; 24540</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6922; 17956</t>
+          <t>6845; 17396</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19076; 35275</t>
+          <t>19449; 35299</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11986; 24817</t>
+          <t>11510; 25294</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16854; 32322</t>
+          <t>17329; 33111</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>44175; 66638</t>
+          <t>43786; 66645</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26344; 45078</t>
+          <t>26230; 45458</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP42B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,03%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>24,8%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,96%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,14</t>
+          <t>0,0; 24,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 46,88</t>
+          <t>19,73; 65,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 25,43</t>
+          <t>3,57; 34,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,51</t>
+          <t>0,0; 30,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,4; 65,91</t>
+          <t>9,57; 50,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 31,18</t>
+          <t>2,71; 27,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,76</t>
+          <t>0,0; 17,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 49,42</t>
+          <t>19,94; 49,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 23,2</t>
+          <t>5,02; 22,43</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>15,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>15,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,26%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 34,62</t>
+          <t>0,0; 12,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 27,28</t>
+          <t>7,09; 25,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 24,78</t>
+          <t>2,59; 16,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>3,88; 35,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,39; 27,17</t>
+          <t>7,68; 27,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 17,75</t>
+          <t>5,65; 24,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,57</t>
+          <t>3,3; 18,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 22,75</t>
+          <t>9,34; 23,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,89</t>
+          <t>5,43; 16,66</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8,88%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,06%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,41</t>
+          <t>0,0; 29,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,68</t>
+          <t>0,0; 11,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,37</t>
+          <t>0,0; 21,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,26</t>
+          <t>0,0; 20,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,62</t>
+          <t>0,0; 10,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 16,16</t>
+          <t>2,14; 18,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 10,22</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,58%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 37,19</t>
+          <t>0,0; 17,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 44,62</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,81</t>
+          <t>5,13; 27,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,9</t>
+          <t>4,49; 37,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,33</t>
+          <t>11,77; 44,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 28,37</t>
+          <t>0,0; 17,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 21,96</t>
+          <t>2,68; 20,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 24,93</t>
+          <t>6,3; 25,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 18,21</t>
+          <t>4,3; 18,48</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>18,68%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>30,66%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,38%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 59,54</t>
+          <t>0,0; 45,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,89</t>
+          <t>0,0; 15,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 77,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,86</t>
+          <t>7,5; 58,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,2</t>
+          <t>0,0; 19,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,6</t>
+          <t>0,0; 42,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,32; 41,0</t>
+          <t>8,18; 44,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,47</t>
+          <t>0,0; 11,01</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>9,77%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>11,68%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4,95%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 24,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,53</t>
+          <t>2,74; 28,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,6</t>
+          <t>0,0; 36,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,08; 26,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 28,77</t>
+          <t>0,0; 33,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,75</t>
+          <t>0,0; 24,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,46</t>
+          <t>1,6; 14,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 26,52</t>
+          <t>3,43; 23,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 24,82</t>
+          <t>2,62; 24,77</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22,1%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,37%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>20,48%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10,11%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,87</t>
+          <t>5,31; 26,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 32,09</t>
+          <t>12,65; 34,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 21,15</t>
+          <t>1,32; 11,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 26,75</t>
+          <t>0,0; 15,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,44; 34,57</t>
+          <t>11,71; 33,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,36</t>
+          <t>3,68; 20,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 17,03</t>
+          <t>4,49; 17,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,35; 30,04</t>
+          <t>14,8; 30,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 12,74</t>
+          <t>3,07; 12,07</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20,21%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>5,95%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>5,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>8,6%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20,21%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,71</t>
+          <t>10,11; 35,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,71</t>
+          <t>1,57; 14,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,31; 18,23</t>
+          <t>1,73; 16,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,98; 34,55</t>
+          <t>0,0; 19,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,87</t>
+          <t>1,64; 14,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 15,42</t>
+          <t>3,5; 17,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,01; 23,42</t>
+          <t>6,92; 22,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 11,37</t>
+          <t>2,57; 12,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,25</t>
+          <t>3,88; 13,13</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,5</t>
+          <t>4,37; 10,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,99</t>
+          <t>10,09; 18,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,14</t>
+          <t>4,81; 10,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,82</t>
+          <t>5,52; 13,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,77</t>
+          <t>11,54; 20,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,78</t>
+          <t>5,69; 12,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,15</t>
+          <t>5,83; 10,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,94; 18,17</t>
+          <t>11,98; 17,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,41</t>
+          <t>5,96; 10,07</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1760,27 +1760,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5696</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>3181</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1744</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5696</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2820</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2833</t>
+          <t>0; 3961</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1079; 6012</t>
+          <t>2682; 8913</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>446; 4452</t>
+          <t>705; 6777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4012</t>
+          <t>0; 2948</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2773; 8961</t>
+          <t>1228; 6468</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>639; 6161</t>
+          <t>475; 4850</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5417</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5141; 13057</t>
+          <t>5267; 13131</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2164; 8647</t>
+          <t>1870; 8358</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2575</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5230</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4485</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5169</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>658; 5711</t>
+          <t>0; 2620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2538; 9173</t>
+          <t>2476; 8781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1870; 8385</t>
+          <t>1111; 6994</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3398</t>
+          <t>639; 5843</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2579; 9484</t>
+          <t>2583; 9121</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1339; 7621</t>
+          <t>1912; 8418</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1271; 7024</t>
+          <t>1250; 7066</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6417; 15588</t>
+          <t>6404; 15924</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4606; 12969</t>
+          <t>4165; 12791</t>
         </is>
       </c>
     </row>
@@ -2081,27 +2081,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>759</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4937</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3619</t>
+          <t>0; 4439</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4128</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4352</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3284</t>
+          <t>0; 3819</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4369</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>641; 5005</t>
+          <t>661; 5596</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4348</t>
+          <t>0; 4390</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3946</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2376</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4682</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1399</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3946</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>651; 5432</t>
+          <t>0; 3246</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1988; 8357</t>
+          <t>0; 4254</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4715</t>
+          <t>1524; 8133</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3449</t>
+          <t>655; 5538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2817</t>
+          <t>2205; 8317</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1455; 8436</t>
+          <t>0; 4327</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>859; 7213</t>
+          <t>880; 6870</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2540; 9567</t>
+          <t>2417; 9800</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2219; 9981</t>
+          <t>2357; 10128</t>
         </is>
       </c>
     </row>
@@ -2407,27 +2407,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3021</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>688</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2647</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>714; 5866</t>
+          <t>0; 3736</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3590</t>
+          <t>0; 3409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3139</t>
+          <t>739; 5717</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3345</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2622</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1510; 7439</t>
+          <t>1484; 8062</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>0; 4150</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>608</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1667</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1507</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>629; 5067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3579</t>
+          <t>436; 4593</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3144</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>638; 5451</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>455; 4587</t>
+          <t>0; 3484</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4632</t>
+          <t>0; 3054</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>641; 5774</t>
+          <t>638; 5628</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1141; 6977</t>
+          <t>903; 6124</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>610; 5739</t>
+          <t>607; 5726</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4107</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1352</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>8255</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3399</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4107</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>8240</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1886</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4601</t>
+          <t>1533; 7697</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4302; 12935</t>
+          <t>4718; 12750</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1307; 7106</t>
+          <t>583; 4947</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1400; 7717</t>
+          <t>0; 4703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4640; 12889</t>
+          <t>4720; 13619</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>584; 5007</t>
+          <t>1238; 7030</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2663; 10182</t>
+          <t>2684; 10237</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11134; 23312</t>
+          <t>11484; 23631</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2515; 9899</t>
+          <t>2388; 9379</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>1432</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3947</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5547</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2611</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4265</t>
+          <t>2775; 9626</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>590; 5053</t>
+          <t>685; 6235</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1519; 8368</t>
+          <t>700; 6715</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2739; 9484</t>
+          <t>0; 4585</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>684; 6473</t>
+          <t>603; 5437</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>656; 6233</t>
+          <t>1606; 8049</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4127; 12068</t>
+          <t>3565; 11812</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2061; 9140</t>
+          <t>2069; 9870</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3465; 11439</t>
+          <t>3347; 11329</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>12496</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>28224</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>17029</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>17567</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>7944; 18363</t>
+          <t>7026; 17578</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>21221; 37511</t>
+          <t>18970; 35036</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12180; 24540</t>
+          <t>11284; 24965</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6845; 17396</t>
+          <t>7509; 18963</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19449; 35299</t>
+          <t>20630; 36151</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11510; 25294</t>
+          <t>11500; 24287</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17329; 33111</t>
+          <t>17297; 31965</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>43786; 66645</t>
+          <t>43936; 65513</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26230; 45458</t>
+          <t>26016; 43951</t>
         </is>
       </c>
     </row>
